--- a/StartFromHere.xlsx
+++ b/StartFromHere.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lorh/Desktop/Automated_Invoice/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lorh/Desktop/automated_invoice/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE5F8870-F073-6543-9B67-8CAD0A850C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFC9E5E6-46B8-674E-B894-7850E7161F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3540" yWindow="500" windowWidth="22200" windowHeight="15800" xr2:uid="{F8A594F3-A53D-3F4E-8D9B-D4DE027352B9}"/>
   </bookViews>
@@ -590,7 +590,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
